--- a/front/Template-products.xlsx
+++ b/front/Template-products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Galvis Personal\Documents\inventory scanner\front\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0090473-8E91-4370-9567-6B71962B229E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF698891-C8B2-49DD-8AA2-9C8BCABFF26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{99A7F6B7-DD8C-4095-A6DD-53DEFB852039}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{99A7F6B7-DD8C-4095-A6DD-53DEFB852039}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -75,6 +75,15 @@
   </si>
   <si>
     <t>El codigo del producto se generará de forma automática basado en los productos existentes</t>
+  </si>
+  <si>
+    <t>Ref Proveedor</t>
+  </si>
+  <si>
+    <t>Referencia Proveedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduzca el codigo de referencia con el que el producto viene desde el proveedor </t>
   </si>
 </sst>
 </file>
@@ -204,6 +213,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -215,12 +230,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -538,124 +547,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC4AB368-B3CF-4C05-905B-367687EA1AA1}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="8" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -664,15 +689,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CBDD1F-5CDF-4473-A6C7-548C17A4BADD}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,6 +707,9 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
